--- a/metadata/CategoriesAndTags.xlsx
+++ b/metadata/CategoriesAndTags.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomar\source\repos\technical-blog\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BEE89B-0D87-46F6-89BF-B7BBA48704C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7576891F-BAD7-441B-84A6-12D2E6109011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{71938F04-02B6-4E0B-A9C3-9D48821FDDCD}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{71938F04-02B6-4E0B-A9C3-9D48821FDDCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Categories" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="109">
   <si>
     <t>rain-paradox</t>
   </si>
@@ -63,9 +63,6 @@
     <t>Tag</t>
   </si>
   <si>
-    <t>five-second-rule-explored</t>
-  </si>
-  <si>
     <t>SymPy</t>
   </si>
   <si>
@@ -349,6 +346,24 @@
   </si>
   <si>
     <t>Inside Attention, Part 1: The Mechanism</t>
+  </si>
+  <si>
+    <t>induction heads</t>
+  </si>
+  <si>
+    <t>interpretability</t>
+  </si>
+  <si>
+    <t>how-large-language-models-learn</t>
+  </si>
+  <si>
+    <t>how-large-language-models-read-code</t>
+  </si>
+  <si>
+    <t>how-large-language-models-think</t>
+  </si>
+  <si>
+    <t>how-large-language-models-tokenize-text</t>
   </si>
 </sst>
 </file>
@@ -422,7 +437,22 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -440,22 +470,7 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -483,9 +498,9 @@
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{F23996D8-E038-415A-AB46-54564A371285}" name="Category"/>
-    <tableColumn id="2" xr3:uid="{39A3421C-15E2-433F-BE66-3D63EEDD4687}" name="Post" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{39A3421C-15E2-433F-BE66-3D63EEDD4687}" name="Post" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{C02648FB-67D5-4ADC-9EBC-5B72CAD5619A}" name="Title"/>
-    <tableColumn id="4" xr3:uid="{98EF9C75-81CD-4D8A-B580-7C33356E2373}" name="URL" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{98EF9C75-81CD-4D8A-B580-7C33356E2373}" name="URL" dataDxfId="0">
       <calculatedColumnFormula>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -494,14 +509,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{07C3CC26-95B6-4B44-8B92-969D553E6E58}" name="Table3" displayName="Table3" ref="A1:B94" totalsRowShown="0">
-  <autoFilter ref="A1:B94" xr:uid="{07C3CC26-95B6-4B44-8B92-969D553E6E58}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B94">
-    <sortCondition ref="B2:B94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{07C3CC26-95B6-4B44-8B92-969D553E6E58}" name="Table3" displayName="Table3" ref="A1:B101" totalsRowShown="0">
+  <autoFilter ref="A1:B101" xr:uid="{07C3CC26-95B6-4B44-8B92-969D553E6E58}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B101">
+    <sortCondition ref="B2:B101"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{7A38640D-FB54-4A3A-B307-2BCDCDCF5A4D}" name="Tag"/>
-    <tableColumn id="2" xr3:uid="{9FA29049-8E81-4079-9D9A-737CCB3015ED}" name="Post" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{9FA29049-8E81-4079-9D9A-737CCB3015ED}" name="Post" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -844,21 +859,21 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
         <v>81</v>
-      </c>
-      <c r="C2" t="s">
-        <v>82</v>
       </c>
       <c r="D2" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -867,13 +882,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
         <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
       </c>
       <c r="D3" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -882,13 +897,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
         <v>83</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
       </c>
       <c r="D4" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -897,13 +912,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -912,13 +927,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -927,13 +942,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -942,13 +957,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -957,13 +972,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" t="s">
         <v>102</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
       </c>
       <c r="D9" s="3" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -972,13 +987,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
         <v>85</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
       </c>
       <c r="D10" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -987,13 +1002,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1002,13 +1017,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
         <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
       </c>
       <c r="D12" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1017,13 +1032,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1032,13 +1047,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1047,13 +1062,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1062,13 +1077,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
         <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
       </c>
       <c r="D16" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1077,13 +1092,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1092,13 +1107,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1107,13 +1122,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
         <v>67</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
       </c>
       <c r="D19" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1122,13 +1137,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1137,13 +1152,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1152,13 +1167,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1167,13 +1182,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="2" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://tomarcher.io/posts/",Table2[[#This Row],[Post]]))</f>
@@ -1190,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A5A7A2-6C88-4B5B-9CA2-1FC13B12127A}">
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
@@ -1212,34 +1227,34 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1247,71 +1262,71 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1319,39 +1334,39 @@
         <v>3</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1359,335 +1374,335 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="B57" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -1695,7 +1710,7 @@
         <v>29</v>
       </c>
       <c r="B62" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -1703,55 +1718,55 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B66" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B68" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -1759,167 +1774,167 @@
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B73" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="B75" t="s">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="B78" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B82" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B86" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="B87" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="B88" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -1927,30 +1942,86 @@
         <v>16</v>
       </c>
       <c r="B91" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B92" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>32</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>23</v>
+      </c>
+      <c r="B95" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>3</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B96" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>35</v>
+      </c>
+      <c r="B97" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>24</v>
+      </c>
+      <c r="B99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>29</v>
+      </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" t="s">
         <v>5</v>
       </c>
     </row>
